--- a/docs/shivacha-leads-template.xlsx
+++ b/docs/shivacha-leads-template.xlsx
@@ -101,10 +101,10 @@
     <t>Sales team: update Lead Status (dropdown), Assigned Sales Person, Notes, Last Contacted and Next Follow-up.</t>
   </si>
   <si>
-    <t>Statuses: New → Contacted → Qualified → Proposal Sent → Negotiation → Won → Lost → Follow-up</t>
+    <t>Statuses: New → Contacted → Qualified → Meeting → Proposal → Negotiation → Won → Lost → Nurture</t>
   </si>
   <si>
-    <t>Lead Score: 0–100 (Hot ≥ 70, Warm ≥ 45, otherwise Cold) — budget, service, work email, phone, company and description detail.</t>
+    <t>Lead Score: 0–100 (Hot ≥ 70, Warm ≥ 45, otherwise Nurture) — budget, service, work email, phone, company, description detail and engagement.</t>
   </si>
   <si>
     <t>Times are in UTC (India = UTC + 5:30).</t>
@@ -5697,7 +5697,7 @@
       <formula>NOT(ISERROR(SEARCH("Qualified",Q2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="4">
-      <formula>NOT(ISERROR(SEARCH("Proposal Sent",Q2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Proposal",Q2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="5">
       <formula>NOT(ISERROR(SEARCH("Negotiation",Q2)))</formula>
@@ -5709,15 +5709,15 @@
       <formula>NOT(ISERROR(SEARCH("Lost",Q2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="7" priority="8">
-      <formula>NOT(ISERROR(SEARCH("Follow-up",Q2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Nurture",Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lead Status" error="Choose a status from the list." sqref="Q10:Q5000">
-      <formula1>"New,Contacted,Qualified,Proposal Sent,Negotiation,Won,Lost,Follow-up"</formula1>
+      <formula1>"New,Contacted,Qualified,Meeting,Proposal,Negotiation,Won,Lost,Nurture"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Lead Status" error="Choose a status from the list." sqref="Q2:Q5000">
-      <formula1>"New,Contacted,Qualified,Proposal Sent,Negotiation,Won,Lost,Follow-up"</formula1>
+      <formula1>"New,Contacted,Qualified,Meeting,Proposal,Negotiation,Won,Lost,Nurture"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
